--- a/agriculture 46.xlsx
+++ b/agriculture 46.xlsx
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
-  <si>
-    <t xml:space="preserve">                  Annual /growth Rate State-wise Area Statistics of Cashew in India(1962-2021)</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
   <si>
     <t xml:space="preserve">Year</t>
   </si>
@@ -264,11 +261,12 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.00"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -284,14 +282,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="14"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -382,7 +372,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -394,15 +384,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -410,7 +400,7 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -431,258 +421,261 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N59"/>
-  <sheetFormatPr defaultColWidth="10.76953125" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:N1048576"/>
+  <sheetFormatPr defaultColWidth="10.78515625" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="1" customFormat="true" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-    </row>
-    <row r="2" s="2" customFormat="true" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="N2" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
+      <c r="B3" s="3" t="n">
+        <v>16.8649405178446</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>8.08314087759814</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>8.08314087759814</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>7.45920745920747</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>8.91463107529589</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>113.725490196078</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>16.8649405178446</v>
+        <v>-2.09580838323352</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>8.08314087759814</v>
+        <v>-2.56410256410257</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>8.08314087759814</v>
+        <v>-2.56410256410257</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>7.45920745920747</v>
+        <v>45.7700650759219</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>8.91463107529589</v>
+        <v>-1.34104046242775</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>113.725490196078</v>
+        <v>-27.5229357798165</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-2.09580838323352</v>
+        <v>-10.0305810397554</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>-2.56410256410257</v>
+        <v>-1.09649122807017</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-2.56410256410257</v>
+        <v>-1.09649122807017</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>45.7700650759219</v>
+        <v>0</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-1.34104046242775</v>
+        <v>7.03070072650573</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>-27.5229357798165</v>
+        <v>17.7215189873418</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>-10.0305810397554</v>
+        <v>23.9292997960571</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-1.09649122807017</v>
+        <v>-4.32372505543236</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-1.09649122807017</v>
+        <v>-4.32372505543236</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0</v>
+        <v>26.4880952380952</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0</v>
+        <v>10.4166666666667</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>7.03070072650573</v>
+        <v>-0.85395226625794</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>17.7215189873418</v>
+        <v>7.5268817204301</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>23.9292997960571</v>
+        <v>6.5825562260011</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-4.32372505543236</v>
+        <v>17.4971031286211</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-4.32372505543236</v>
+        <v>17.4971031286211</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>26.4880952380952</v>
+        <v>7.1764705882353</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>10.4166666666667</v>
+        <v>0</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.85395226625794</v>
+        <v>-1.08215547703181</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>7.5268817204301</v>
+        <v>8.00000000000001</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B8" s="3" t="n">
-        <v>6.5825562260011</v>
+        <v>5.09521358723624</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>17.4971031286211</v>
+        <v>21.4003944773175</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>17.4971031286211</v>
+        <v>21.4003944773175</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>7.1764705882353</v>
+        <v>5.37870472008781</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-1.08215547703181</v>
+        <v>11.2971645456575</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>8.00000000000001</v>
+        <v>4.62962962962961</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>5.09521358723624</v>
+        <v>-4.26052889324192</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>21.4003944773175</v>
+        <v>58.6515028432169</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>21.4003944773175</v>
+        <v>58.6515028432169</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>5.37870472008781</v>
+        <v>0</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0</v>
+        <v>-13.8364779874214</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>11.2971645456575</v>
+        <v>3.3099297893681</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>4.62962962962961</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B10" s="3" t="n">
-        <v>-4.26052889324192</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>58.6515028432169</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>58.6515028432169</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="4" t="n">
-        <v>-13.8364779874214</v>
-      </c>
-      <c r="K10" s="4" t="n">
-        <v>3.3099297893681</v>
-      </c>
-      <c r="L10" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="3" t="n">
-        <v>-100</v>
+      <c r="B11" s="3" t="e">
+        <f aca="false">#DIV/0!</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
@@ -692,7 +685,7 @@
       <c r="L11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B12" s="3" t="e">
@@ -707,7 +700,7 @@
       <c r="L12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B13" s="3" t="e">
@@ -722,281 +715,296 @@
       <c r="L13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="3" t="e">
-        <f aca="false">#DIV/0!</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
+      <c r="B14" s="3" t="n">
+        <v>1.67845748370092</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>0.681909346169252</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>0.681909346169252</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>13.627489262007</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>0.681176275128759</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>0.444352588612174</v>
+      </c>
       <c r="L14" s="4"/>
+      <c r="M14" s="4" t="n">
+        <v>1.44927536231882</v>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>2.90294627383016</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>1.67845748370092</v>
+        <v>61.0914051841746</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.681909346169252</v>
+        <v>11.4209827357238</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.681909346169252</v>
+        <v>11.4209827357238</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>13.627489262007</v>
+        <v>14.6048109965636</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.681176275128759</v>
+        <v>68.0693069306931</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.444352588612174</v>
+        <v>-20.4115226337449</v>
       </c>
       <c r="L15" s="4"/>
       <c r="M15" s="4" t="n">
-        <v>1.44927536231882</v>
+        <v>24</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>2.90294627383016</v>
+        <v>4.42105263157895</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>61.0914051841746</v>
+        <v>2.47289972899729</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>11.4209827357238</v>
+        <v>1.31108462455303</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>11.4209827357238</v>
+        <v>1.31108462455303</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>14.6048109965636</v>
+        <v>19.9400299850075</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>68.0693069306931</v>
+        <v>3.09278350515465</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-20.4115226337449</v>
+        <v>2.11995863495347</v>
       </c>
       <c r="L16" s="4"/>
       <c r="M16" s="4" t="n">
-        <v>24</v>
+        <v>3.68663594470047</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>4.42105263157895</v>
+        <v>2.82258064516128</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>2.47289972899729</v>
+        <v>0.0826446280991711</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.31108462455303</v>
+        <v>2.35294117647058</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.31108462455303</v>
+        <v>2.35294117647058</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>19.9400299850075</v>
+        <v>29.375</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>3.09278350515465</v>
+        <v>3.42857142857143</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>2.11995863495347</v>
+        <v>1.8987341772152</v>
       </c>
       <c r="L17" s="4"/>
       <c r="M17" s="4" t="n">
-        <v>3.68663594470047</v>
+        <v>0</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>2.82258064516128</v>
+        <v>1.96078431372548</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.0826446280991711</v>
+        <v>-16.597853014038</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>2.35294117647058</v>
+        <v>2.29885057471264</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2.35294117647058</v>
+        <v>2.29885057471264</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>29.375</v>
+        <v>14.975845410628</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>3.42857142857143</v>
+        <v>4.97237569060773</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.8987341772152</v>
+        <v>3.1055900621118</v>
       </c>
       <c r="L18" s="4"/>
       <c r="M18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.96078431372548</v>
+        <v>1.92307692307692</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>-16.597853014038</v>
+        <v>1.98019801980198</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.29885057471264</v>
+        <v>2.24719101123596</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2.29885057471264</v>
+        <v>2.24719101123596</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>14.975845410628</v>
+        <v>1.68067226890756</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>4.97237569060773</v>
+        <v>-26.3157894736842</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>3.1055900621118</v>
+        <v>2.40963855421688</v>
       </c>
       <c r="L19" s="4"/>
       <c r="M19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.92307692307692</v>
+        <v>1.88679245283019</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1.98019801980198</v>
+        <v>26.2135922330097</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.24719101123596</v>
+        <v>0</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2.24719101123596</v>
+        <v>0</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.68067226890756</v>
+        <v>0</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-26.3157894736842</v>
+        <v>7.14285714285714</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2.40963855421688</v>
+        <v>1.17647058823529</v>
       </c>
       <c r="L20" s="4"/>
       <c r="M20" s="4" t="n">
-        <v>0</v>
+        <v>-11.1111111111111</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.88679245283019</v>
+        <v>1.85185185185186</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>26.2135922330097</v>
+        <v>3.84615384615385</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0</v>
+        <v>-1.0989010989011</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0</v>
+        <v>-1.0989010989011</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0</v>
+        <v>18.1818181818182</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>7.14285714285714</v>
+        <v>22.2222222222222</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.17647058823529</v>
+        <v>4.65116279069768</v>
       </c>
       <c r="L21" s="4"/>
       <c r="M21" s="4" t="n">
-        <v>-11.1111111111111</v>
+        <v>12.5</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.85185185185186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B22" s="3" t="n">
-        <v>3.84615384615385</v>
+        <v>0.740740740740731</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.0989010989011</v>
+        <v>2.22222222222221</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.0989010989011</v>
+        <v>2.22222222222221</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>18.1818181818182</v>
+        <v>3.4965034965035</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>22.2222222222222</v>
+        <v>9.09090909090908</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>4.65116279069768</v>
+        <v>2.22222222222221</v>
       </c>
       <c r="L22" s="4"/>
       <c r="M22" s="4" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="N22" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.740740740740731</v>
+        <v>0</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2.22222222222221</v>
+        <v>2.17391304347827</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>2.22222222222221</v>
+        <v>2.17391304347827</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>3.4965034965035</v>
+        <v>0</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>9.09090909090908</v>
+        <v>3.33333333333334</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2.22222222222221</v>
+        <v>3.26086956521738</v>
       </c>
       <c r="L23" s="4"/>
       <c r="M23" s="4" t="n">
@@ -1007,26 +1015,26 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="3" t="n">
-        <v>0</v>
+        <v>10.2941176470588</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>2.17391304347827</v>
+        <v>1.06382978723405</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2.17391304347827</v>
+        <v>1.06382978723405</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0</v>
+        <v>8.10810810810811</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>3.33333333333334</v>
+        <v>1.61290322580645</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>3.26086956521738</v>
+        <v>10.5263157894737</v>
       </c>
       <c r="L24" s="4"/>
       <c r="M24" s="4" t="n">
@@ -1037,89 +1045,92 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>10.2941176470588</v>
+        <v>13.3333333333333</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.06382978723405</v>
+        <v>5.26315789473684</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.06382978723405</v>
+        <v>5.26315789473684</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>8.10810810810811</v>
+        <v>0</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.61290322580645</v>
+        <v>-4.76190476190477</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>10.5263157894737</v>
+        <v>15.2380952380952</v>
       </c>
       <c r="L25" s="4"/>
       <c r="M25" s="4" t="n">
-        <v>0</v>
+        <v>11.1111111111111</v>
       </c>
       <c r="N25" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B26" s="3" t="n">
-        <v>13.3333333333333</v>
+        <v>0.588235294117645</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>5.26315789473684</v>
+        <v>2</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>5.26315789473684</v>
+        <v>2</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0</v>
+        <v>2.49999999999999</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-4.76190476190477</v>
+        <v>4.16666666666667</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>15.2380952380952</v>
+        <v>1.65289256198347</v>
       </c>
       <c r="L26" s="4"/>
       <c r="M26" s="4" t="n">
-        <v>11.1111111111111</v>
+        <v>0</v>
       </c>
       <c r="N26" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.588235294117645</v>
+        <v>0</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2</v>
+        <v>0.980392156862742</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2</v>
+        <v>0.980392156862742</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2.49999999999999</v>
+        <v>1.82926829268293</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>4.16666666666667</v>
+        <v>4.8</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.65289256198347</v>
+        <v>0</v>
       </c>
       <c r="L27" s="4"/>
       <c r="M27" s="4" t="n">
@@ -1130,323 +1141,332 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>6.4327485380117</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.980392156862742</v>
+        <v>3.88349514563107</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.980392156862742</v>
+        <v>3.88349514563107</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.82926829268293</v>
+        <v>1.79640718562875</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>4.8</v>
+        <v>4.58015267175573</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0</v>
+        <v>6.5040650406504</v>
       </c>
       <c r="L28" s="4"/>
       <c r="M28" s="4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N28" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>6.4327485380117</v>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>50</v>
-      </c>
+        <v>0.549450549450548</v>
+      </c>
+      <c r="D29" s="3"/>
       <c r="F29" s="4" t="n">
-        <v>3.88349514563107</v>
+        <v>10.2803738317757</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>3.88349514563107</v>
+        <v>10.2803738317757</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.79640718562875</v>
+        <v>2.94117647058822</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>4.58015267175573</v>
+        <v>4.37956204379562</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>6.5040650406504</v>
+        <v>1.52671755725191</v>
       </c>
       <c r="L29" s="4"/>
       <c r="M29" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N29" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="2" t="s">
         <v>42</v>
       </c>
       <c r="B30" s="3" t="n">
-        <v>0.549450549450548</v>
+        <v>0</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="D30" s="3"/>
       <c r="F30" s="4" t="n">
-        <v>10.2803738317757</v>
+        <v>0.847457627118642</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>10.2803738317757</v>
+        <v>0.847457627118642</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>2.94117647058822</v>
+        <v>3.42857142857143</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>4.37956204379562</v>
+        <v>4.19580419580419</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>1.52671755725191</v>
+        <v>1.50375939849625</v>
       </c>
       <c r="L30" s="4"/>
       <c r="M30" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0</v>
+        <v>1.81818181818181</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>0.546448087431695</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="3"/>
+        <v>-59.0909090909091</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>7.04225352112675</v>
+      </c>
       <c r="F31" s="4" t="n">
-        <v>0.847457627118642</v>
+        <v>1.93277310924369</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.847457627118642</v>
+        <v>1.93277310924369</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>3.42857142857143</v>
+        <v>1.10497237569061</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>4.19580419580419</v>
+        <v>5.70469798657718</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>1.50375939849625</v>
+        <v>1.03703703703704</v>
       </c>
       <c r="L31" s="4"/>
       <c r="M31" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N31" s="4" t="n">
+        <v>2.67857142857142</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>5.26315789473684</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>9.52380952380953</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>0.65952184666116</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>0.65952184666116</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>0.655737704918025</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="J32" s="4" t="n">
+        <v>4.06349206349206</v>
+      </c>
+      <c r="K32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="4" t="n">
+        <v>5.12820512820513</v>
+      </c>
+      <c r="M32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>0.543478260869557</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>0.740740740740731</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>1.63800163800163</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>1.63800163800163</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="4" t="n">
+        <v>1.83038438071994</v>
+      </c>
+      <c r="K33" s="4" t="n">
+        <v>2.19941348973607</v>
+      </c>
+      <c r="L33" s="4" t="n">
+        <v>2.4390243902439</v>
+      </c>
+      <c r="M33" s="4" t="n">
         <v>1.81818181818181</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="B32" s="3" t="n">
-        <v>0.546448087431695</v>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>-59.0909090909091</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>7.04225352112675</v>
-      </c>
-      <c r="F32" s="4" t="n">
-        <v>1.93277310924369</v>
-      </c>
-      <c r="G32" s="4" t="n">
-        <v>1.93277310924369</v>
-      </c>
-      <c r="H32" s="4" t="n">
-        <v>1.10497237569061</v>
-      </c>
-      <c r="J32" s="4" t="n">
-        <v>5.70469798657718</v>
-      </c>
-      <c r="K32" s="4" t="n">
-        <v>1.03703703703704</v>
-      </c>
-      <c r="L32" s="4"/>
-      <c r="M32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="4" t="n">
-        <v>2.67857142857142</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="B33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>5.26315789473684</v>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>9.52380952380953</v>
-      </c>
-      <c r="F33" s="4" t="n">
-        <v>0.65952184666116</v>
-      </c>
-      <c r="G33" s="4" t="n">
-        <v>0.65952184666116</v>
-      </c>
-      <c r="H33" s="4" t="n">
-        <v>0.655737704918025</v>
-      </c>
-      <c r="I33" s="4" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="J33" s="4" t="n">
-        <v>4.06349206349206</v>
-      </c>
-      <c r="K33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="4" t="n">
-        <v>5.12820512820513</v>
-      </c>
-      <c r="M33" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="N33" s="4" t="n">
-        <v>0</v>
+        <v>0.869565217391299</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0.543478260869557</v>
+        <v>0.24324324324323</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.740740740740731</v>
+        <v>0.735294117647056</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>20</v>
+        <v>7.46376811594203</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1.63800163800163</v>
+        <v>0.491539081385972</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1.63800163800163</v>
+        <v>0.491539081385972</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0</v>
+        <v>1.085776330076</v>
       </c>
       <c r="I34" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>1.83038438071994</v>
+        <v>8.09466746554823</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>2.19941348973607</v>
+        <v>0.731707317073149</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>2.4390243902439</v>
+        <v>1.19047619047619</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>1.81818181818181</v>
-      </c>
-      <c r="N34" s="4" t="n">
-        <v>0.869565217391299</v>
-      </c>
+        <v>1.42857142857142</v>
+      </c>
+      <c r="N34" s="4"/>
     </row>
     <row r="35" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>0.24324324324323</v>
+        <v>0.0647074683203019</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.735294117647056</v>
+        <v>0</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>5.25</v>
+        <v>-14.2517814726841</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>7.46376811594203</v>
+        <v>0</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.491539081385972</v>
+        <v>0.922139363322905</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.491539081385972</v>
+        <v>0.922139363322905</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1.085776330076</v>
+        <v>0</v>
       </c>
       <c r="I35" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>8.09466746554823</v>
+        <v>1.38573249819856</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.731707317073149</v>
+        <v>0.648055832502514</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>1.19047619047619</v>
+        <v>0</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>1.42857142857142</v>
+        <v>0</v>
       </c>
       <c r="N35" s="4"/>
     </row>
     <row r="36" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="A36" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.0647074683203019</v>
+        <v>0</v>
       </c>
       <c r="C36" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>-14.2517814726841</v>
+        <v>0</v>
       </c>
       <c r="E36" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.922139363322905</v>
+        <v>1.58906721754331</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.922139363322905</v>
+        <v>1.58906721754331</v>
       </c>
       <c r="H36" s="4" t="n">
         <v>0</v>
@@ -1455,10 +1475,10 @@
         <v>0</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>1.38573249819856</v>
+        <v>0.224153955497242</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0.648055832502514</v>
+        <v>0.176890964409537</v>
       </c>
       <c r="L36" s="4" t="n">
         <v>0</v>
@@ -1469,38 +1489,38 @@
       <c r="N36" s="4"/>
     </row>
     <row r="37" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="A37" s="2" t="s">
         <v>49</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>0</v>
+        <v>0.652045050385297</v>
       </c>
       <c r="C37" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0</v>
+        <v>0.415512465373968</v>
       </c>
       <c r="E37" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>1.58906721754331</v>
+        <v>0.938526513374005</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>1.58906721754331</v>
+        <v>0.938526513374005</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>0</v>
+        <v>2.81954887218046</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>0</v>
+        <v>0.941176470588245</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>0.224153955497242</v>
+        <v>5.820423303513</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>0.176890964409537</v>
+        <v>0.494420115835559</v>
       </c>
       <c r="L37" s="4" t="n">
         <v>0</v>
@@ -1511,38 +1531,38 @@
       <c r="N37" s="4"/>
     </row>
     <row r="38" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
+      <c r="A38" s="2" t="s">
         <v>50</v>
       </c>
       <c r="B38" s="3" t="n">
-        <v>0.652045050385297</v>
+        <v>2.40389763357962</v>
       </c>
       <c r="C38" s="4" t="n">
-        <v>0</v>
+        <v>125.985401459854</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>0.415512465373968</v>
+        <v>10.0689655172414</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0</v>
+        <v>5.05731625084289</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0.938526513374005</v>
+        <v>0.697350069735014</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>0.938526513374005</v>
+        <v>0.697350069735014</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>2.81954887218046</v>
+        <v>0</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>0.941176470588245</v>
+        <v>2.33100233100232</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>5.820423303513</v>
+        <v>5.87143667199339</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0.494420115835559</v>
+        <v>2.57942086027549</v>
       </c>
       <c r="L38" s="4" t="n">
         <v>0</v>
@@ -1550,163 +1570,129 @@
       <c r="M38" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N38" s="4"/>
+      <c r="N38" s="4" t="n">
+        <v>0.171673819742502</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+      <c r="A39" s="2" t="s">
         <v>51</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>2.40389763357962</v>
+        <v>0.590787891462319</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>125.985401459854</v>
+        <v>0.452196382428949</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>10.0689655172414</v>
+        <v>9.02255639097742</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>5.05731625084289</v>
+        <v>0.128369704749676</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>0.697350069735014</v>
+        <v>1.90058479532165</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>0.697350069735014</v>
+        <v>1.90058479532165</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>0</v>
+        <v>0.0261164794985724</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>2.33100233100232</v>
+        <v>0.227790432801833</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>5.87143667199339</v>
+        <v>4.19709806212873</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>2.57942086027549</v>
+        <v>2.98047276464544</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>0</v>
+        <v>1.17647058823529</v>
       </c>
       <c r="M39" s="4" t="n">
-        <v>0</v>
+        <v>0.352112676056349</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>0.171673819742502</v>
+        <v>0.0856898029134578</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+      <c r="A40" s="2" t="s">
         <v>52</v>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0.590787891462319</v>
+        <v>1.97505197505197</v>
       </c>
       <c r="C40" s="4" t="n">
-        <v>0.452196382428949</v>
+        <v>3.85852090032153</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>9.02255639097742</v>
+        <v>11.4942528735632</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.128369704749676</v>
+        <v>0</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>1.90058479532165</v>
+        <v>3.75292607415238</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>1.90058479532165</v>
+        <v>3.75292607415238</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>0.0261164794985724</v>
+        <v>0</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>0.227790432801833</v>
+        <v>0</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>4.19709806212873</v>
+        <v>0</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>2.98047276464544</v>
+        <v>11.1111111111111</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>1.17647058823529</v>
+        <v>0</v>
       </c>
       <c r="M40" s="4" t="n">
-        <v>0.352112676056349</v>
+        <v>0</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>0.0856898029134578</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+        <v>1.02739726027397</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D41" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B41" s="3" t="n">
-        <v>1.97505197505197</v>
-      </c>
-      <c r="C41" s="4" t="n">
-        <v>3.85852090032153</v>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>11.4942528735632</v>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="4" t="n">
-        <v>3.75292607415238</v>
-      </c>
-      <c r="G41" s="4" t="n">
-        <v>3.75292607415238</v>
-      </c>
-      <c r="H41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="4" t="n">
-        <v>11.1111111111111</v>
-      </c>
-      <c r="L41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" s="4" t="n">
-        <v>1.02739726027397</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D42" s="5" t="s">
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+    </row>
+    <row r="42" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D42" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="5"/>
-    </row>
-    <row r="43" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D43" s="6" t="s">
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
+    </row>
+    <row r="43" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D43" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E43" s="6"/>
-      <c r="F43" s="6"/>
-      <c r="G43" s="6"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="7"/>
+      <c r="G43" s="7"/>
     </row>
     <row r="44" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D44" s="7" t="s">
+      <c r="D44" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
-      <c r="G44" s="7"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8"/>
     </row>
     <row r="45" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D45" s="8" t="s">
@@ -1772,27 +1758,27 @@
       <c r="F52" s="8"/>
       <c r="G52" s="8"/>
     </row>
-    <row r="53" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D53" s="8" t="s">
+    <row r="53" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D53" s="9"/>
+      <c r="E53" s="9"/>
+      <c r="F53" s="9"/>
+      <c r="G53" s="9"/>
+    </row>
+    <row r="54" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D54" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="E53" s="8"/>
-      <c r="F53" s="8"/>
-      <c r="G53" s="8"/>
-    </row>
-    <row r="54" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D54" s="9"/>
       <c r="E54" s="9"/>
       <c r="F54" s="9"/>
       <c r="G54" s="9"/>
     </row>
     <row r="55" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D55" s="9" t="s">
+      <c r="D55" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="E55" s="9"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="9"/>
+      <c r="E55" s="8"/>
+      <c r="F55" s="8"/>
+      <c r="G55" s="8"/>
     </row>
     <row r="56" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D56" s="8" t="s">
@@ -1818,16 +1804,10 @@
       <c r="F58" s="8"/>
       <c r="G58" s="8"/>
     </row>
-    <row r="59" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D59" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E59" s="8"/>
-      <c r="F59" s="8"/>
-      <c r="G59" s="8"/>
-    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="D41:G41"/>
     <mergeCell ref="D42:G42"/>
     <mergeCell ref="D43:G43"/>
     <mergeCell ref="D44:G44"/>
@@ -1845,7 +1825,6 @@
     <mergeCell ref="D56:G56"/>
     <mergeCell ref="D57:G57"/>
     <mergeCell ref="D58:G58"/>
-    <mergeCell ref="D59:G59"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/agriculture 46.xlsx
+++ b/agriculture 46.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
   <si>
     <t xml:space="preserve">Year</t>
   </si>
@@ -179,6 +179,9 @@
   </si>
   <si>
     <t xml:space="preserve">2020-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unit:- </t>
   </si>
   <si>
     <r>
@@ -188,7 +191,6 @@
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Source:</t>
     </r>
@@ -198,25 +200,36 @@
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> EPWRF (Economic and Political Weekly Research Foundation )1962-2021</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Footnote</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">: Telangana:-&gt; On 2 June 2014, Telangana was separated from Andhra Pradesh as the 29th state of India. However Indian Horticulture Database disseminated separate data for both Andhra Pradesh &amp; Telangana in the year 2013-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">:-&gt; Data for Daman and Diu are included under Goa, Daman and Diu for the years 1962-63 To 1979-80.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">:-&gt; Data for Haryana are included under Punjab for the years 1962-63 To 1964-65.</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Description:- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Telangana:-&gt; On 2 June 2014, Telangana was separated from Andhra Pradesh as the 29th state of India. However Indian Horticulture Database disseminated separate data for both Andhra Pradesh &amp; Telangana in the year 2013-14</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Data for Daman and Diu are included under Goa, Daman and Diu for the years 1962-63 To 1979-80.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data for Haryana are included under Punjab for the years 1962-63 To 1964-65.</t>
   </si>
   <si>
     <t xml:space="preserve">1993-94 to 2013-14 - Plantation Crops: Cashewnut: Yield:-&gt; Yield has been calculated for the years 1993-94 To 2013-14.</t>
@@ -237,10 +250,25 @@
     <t xml:space="preserve">Plantation Crops: Cashewnut: Yield:-&gt; Cashewnut Yield is based on the total planted area.</t>
   </si>
   <si>
-    <t xml:space="preserve">Source Description:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1962-63 to 1969-70: Plantation Crops: Cashewnut:-&gt; Directorate of Economics and Statistics, Dept. of Agriculture, Cooperation and Farmers Welfare, Ministry of Agriculture, Govt. of India</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Source Description: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">1962-63 to 1969-70: Plantation Crops: Cashewnut:-&gt; Directorate of Economics and Statistics, Dept. of Agriculture, Cooperation and Farmers Welfare, Ministry of Agriculture, Govt. of India</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">1993-94 to 2007-08: Plantation Crops: Cashewnut:-&gt; Directorate of Cashewnut and Cocoa Development, Ministry of Agriculture and Farmers Welfare, Govt. of India</t>
@@ -261,7 +289,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.00"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -297,14 +325,23 @@
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -315,23 +352,9 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="1">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
       <right/>
       <top/>
       <bottom/>
@@ -363,7 +386,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -384,24 +407,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -422,7 +433,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N1048576"/>
-  <sheetFormatPr defaultColWidth="10.78515625" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -1662,169 +1673,297 @@
         <v>1.02739726027397</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D41" s="5" t="s">
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
-    </row>
-    <row r="42" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D42" s="6" t="s">
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2"/>
+      <c r="N41" s="2"/>
+    </row>
+    <row r="42" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E42" s="6"/>
-      <c r="F42" s="6"/>
-      <c r="G42" s="6"/>
-    </row>
-    <row r="43" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D43" s="7" t="s">
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
+      <c r="I42" s="5"/>
+      <c r="J42" s="5"/>
+      <c r="K42" s="5"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="5"/>
+      <c r="N42" s="5"/>
+    </row>
+    <row r="43" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E43" s="7"/>
-      <c r="F43" s="7"/>
-      <c r="G43" s="7"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="5"/>
+      <c r="J43" s="5"/>
+      <c r="K43" s="5"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="5"/>
+      <c r="N43" s="5"/>
     </row>
     <row r="44" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D44" s="8" t="s">
+      <c r="A44" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
-      <c r="G44" s="8"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6"/>
+      <c r="J44" s="6"/>
+      <c r="K44" s="6"/>
+      <c r="L44" s="6"/>
+      <c r="M44" s="6"/>
+      <c r="N44" s="6"/>
     </row>
     <row r="45" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D45" s="8" t="s">
+      <c r="A45" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
-      <c r="G45" s="8"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="6"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="6"/>
+      <c r="J45" s="6"/>
+      <c r="K45" s="6"/>
+      <c r="L45" s="6"/>
+      <c r="M45" s="6"/>
+      <c r="N45" s="6"/>
     </row>
     <row r="46" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D46" s="8" t="s">
+      <c r="A46" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
-      <c r="G46" s="8"/>
+      <c r="B46" s="6"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="6"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="6"/>
+      <c r="J46" s="6"/>
+      <c r="K46" s="6"/>
+      <c r="L46" s="6"/>
+      <c r="M46" s="6"/>
+      <c r="N46" s="6"/>
     </row>
     <row r="47" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D47" s="8" t="s">
+      <c r="A47" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E47" s="8"/>
-      <c r="F47" s="8"/>
-      <c r="G47" s="8"/>
+      <c r="B47" s="6"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6"/>
+      <c r="G47" s="6"/>
+      <c r="H47" s="6"/>
+      <c r="I47" s="6"/>
+      <c r="J47" s="6"/>
+      <c r="K47" s="6"/>
+      <c r="L47" s="6"/>
+      <c r="M47" s="6"/>
+      <c r="N47" s="6"/>
     </row>
     <row r="48" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D48" s="8" t="s">
+      <c r="A48" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E48" s="8"/>
-      <c r="F48" s="8"/>
-      <c r="G48" s="8"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="6"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="6"/>
+      <c r="J48" s="6"/>
+      <c r="K48" s="6"/>
+      <c r="L48" s="6"/>
+      <c r="M48" s="6"/>
+      <c r="N48" s="6"/>
     </row>
     <row r="49" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D49" s="8" t="s">
+      <c r="A49" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="E49" s="8"/>
-      <c r="F49" s="8"/>
-      <c r="G49" s="8"/>
+      <c r="B49" s="6"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="6"/>
+      <c r="G49" s="6"/>
+      <c r="H49" s="6"/>
+      <c r="I49" s="6"/>
+      <c r="J49" s="6"/>
+      <c r="K49" s="6"/>
+      <c r="L49" s="6"/>
+      <c r="M49" s="6"/>
+      <c r="N49" s="6"/>
     </row>
     <row r="50" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D50" s="8" t="s">
+      <c r="A50" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="E50" s="8"/>
-      <c r="F50" s="8"/>
-      <c r="G50" s="8"/>
+      <c r="B50" s="6"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="6"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="6"/>
+      <c r="J50" s="6"/>
+      <c r="K50" s="6"/>
+      <c r="L50" s="6"/>
+      <c r="M50" s="6"/>
+      <c r="N50" s="6"/>
     </row>
     <row r="51" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D51" s="8" t="s">
+      <c r="A51" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="E51" s="8"/>
-      <c r="F51" s="8"/>
-      <c r="G51" s="8"/>
+      <c r="B51" s="6"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="6"/>
+      <c r="H51" s="6"/>
+      <c r="I51" s="6"/>
+      <c r="J51" s="6"/>
+      <c r="K51" s="6"/>
+      <c r="L51" s="6"/>
+      <c r="M51" s="6"/>
+      <c r="N51" s="6"/>
     </row>
     <row r="52" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D52" s="8" t="s">
+      <c r="A52" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E52" s="8"/>
-      <c r="F52" s="8"/>
-      <c r="G52" s="8"/>
-    </row>
-    <row r="53" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D53" s="9"/>
-      <c r="E53" s="9"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="9"/>
-    </row>
-    <row r="54" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D54" s="9" t="s">
+      <c r="B52" s="5"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="5"/>
+      <c r="I52" s="5"/>
+      <c r="J52" s="5"/>
+      <c r="K52" s="5"/>
+      <c r="L52" s="5"/>
+      <c r="M52" s="5"/>
+      <c r="N52" s="5"/>
+    </row>
+    <row r="53" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E54" s="9"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="9"/>
+      <c r="B53" s="6"/>
+      <c r="C53" s="6"/>
+      <c r="D53" s="6"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="6"/>
+      <c r="G53" s="6"/>
+      <c r="H53" s="6"/>
+      <c r="I53" s="6"/>
+      <c r="J53" s="6"/>
+      <c r="K53" s="6"/>
+      <c r="L53" s="6"/>
+      <c r="M53" s="6"/>
+      <c r="N53" s="6"/>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B54" s="6"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="6"/>
+      <c r="E54" s="6"/>
+      <c r="F54" s="6"/>
+      <c r="G54" s="6"/>
+      <c r="H54" s="6"/>
+      <c r="I54" s="6"/>
+      <c r="J54" s="6"/>
+      <c r="K54" s="6"/>
+      <c r="L54" s="6"/>
+      <c r="M54" s="6"/>
+      <c r="N54" s="6"/>
     </row>
     <row r="55" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D55" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E55" s="8"/>
-      <c r="F55" s="8"/>
-      <c r="G55" s="8"/>
-    </row>
-    <row r="56" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D56" s="8" t="s">
+      <c r="A55" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="E56" s="8"/>
-      <c r="F56" s="8"/>
-      <c r="G56" s="8"/>
-    </row>
-    <row r="57" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D57" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="E57" s="8"/>
-      <c r="F57" s="8"/>
-      <c r="G57" s="8"/>
-    </row>
-    <row r="58" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D58" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="E58" s="8"/>
-      <c r="F58" s="8"/>
-      <c r="G58" s="8"/>
-    </row>
+      <c r="B55" s="6"/>
+      <c r="C55" s="6"/>
+      <c r="D55" s="6"/>
+      <c r="E55" s="6"/>
+      <c r="F55" s="6"/>
+      <c r="G55" s="6"/>
+      <c r="H55" s="6"/>
+      <c r="I55" s="6"/>
+      <c r="J55" s="6"/>
+      <c r="K55" s="6"/>
+      <c r="L55" s="6"/>
+      <c r="M55" s="6"/>
+      <c r="N55" s="6"/>
+    </row>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="D41:G41"/>
-    <mergeCell ref="D42:G42"/>
-    <mergeCell ref="D43:G43"/>
-    <mergeCell ref="D44:G44"/>
-    <mergeCell ref="D45:G45"/>
-    <mergeCell ref="D46:G46"/>
-    <mergeCell ref="D47:G47"/>
-    <mergeCell ref="D48:G48"/>
-    <mergeCell ref="D49:G49"/>
-    <mergeCell ref="D50:G50"/>
-    <mergeCell ref="D51:G51"/>
-    <mergeCell ref="D52:G52"/>
-    <mergeCell ref="D53:G53"/>
-    <mergeCell ref="D54:G54"/>
-    <mergeCell ref="D55:G55"/>
-    <mergeCell ref="D56:G56"/>
-    <mergeCell ref="D57:G57"/>
-    <mergeCell ref="D58:G58"/>
+  <mergeCells count="15">
+    <mergeCell ref="A41:N41"/>
+    <mergeCell ref="A42:N42"/>
+    <mergeCell ref="A43:N43"/>
+    <mergeCell ref="A44:N44"/>
+    <mergeCell ref="A45:N45"/>
+    <mergeCell ref="A46:N46"/>
+    <mergeCell ref="A47:N47"/>
+    <mergeCell ref="A48:N48"/>
+    <mergeCell ref="A49:N49"/>
+    <mergeCell ref="A50:N50"/>
+    <mergeCell ref="A51:N51"/>
+    <mergeCell ref="A52:N52"/>
+    <mergeCell ref="A53:N53"/>
+    <mergeCell ref="A54:N54"/>
+    <mergeCell ref="A55:N55"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/agriculture 46.xlsx
+++ b/agriculture 46.xlsx
@@ -181,7 +181,7 @@
     <t xml:space="preserve">2020-21</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit:- </t>
+    <t xml:space="preserve">Unit:- Percentage(%)</t>
   </si>
   <si>
     <r>
@@ -191,6 +191,7 @@
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Source:</t>
     </r>
@@ -200,6 +201,7 @@
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> EPWRF (Economic and Political Weekly Research Foundation )1962-2021</t>
     </r>
@@ -212,6 +214,7 @@
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Description:- </t>
     </r>
@@ -221,6 +224,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Telangana:-&gt; On 2 June 2014, Telangana was separated from Andhra Pradesh as the 29th state of India. However Indian Horticulture Database disseminated separate data for both Andhra Pradesh &amp; Telangana in the year 2013-14</t>
     </r>
@@ -257,6 +261,7 @@
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Source Description: </t>
     </r>
@@ -266,6 +271,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">1962-63 to 1969-70: Plantation Crops: Cashewnut:-&gt; Directorate of Economics and Statistics, Dept. of Agriculture, Cooperation and Farmers Welfare, Ministry of Agriculture, Govt. of India</t>
     </r>
@@ -289,7 +295,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.00"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -325,23 +331,21 @@
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -407,11 +411,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -433,7 +437,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N1048576"/>
-  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.8125" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -1674,274 +1678,274 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="2" t="s">
+      <c r="A41" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
-      <c r="J41" s="2"/>
-      <c r="K41" s="2"/>
-      <c r="L41" s="2"/>
-      <c r="M41" s="2"/>
-      <c r="N41" s="2"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="5"/>
+      <c r="K41" s="5"/>
+      <c r="L41" s="5"/>
+      <c r="M41" s="5"/>
+      <c r="N41" s="5"/>
     </row>
     <row r="42" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="5" t="s">
+      <c r="A42" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="5"/>
-      <c r="H42" s="5"/>
-      <c r="I42" s="5"/>
-      <c r="J42" s="5"/>
-      <c r="K42" s="5"/>
-      <c r="L42" s="5"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="5"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6"/>
+      <c r="J42" s="6"/>
+      <c r="K42" s="6"/>
+      <c r="L42" s="6"/>
+      <c r="M42" s="6"/>
+      <c r="N42" s="6"/>
     </row>
     <row r="43" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="5" t="s">
+      <c r="A43" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B43" s="5"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="5"/>
-      <c r="H43" s="5"/>
-      <c r="I43" s="5"/>
-      <c r="J43" s="5"/>
-      <c r="K43" s="5"/>
-      <c r="L43" s="5"/>
-      <c r="M43" s="5"/>
-      <c r="N43" s="5"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6"/>
+      <c r="J43" s="6"/>
+      <c r="K43" s="6"/>
+      <c r="L43" s="6"/>
+      <c r="M43" s="6"/>
+      <c r="N43" s="6"/>
     </row>
     <row r="44" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="6" t="s">
+      <c r="A44" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B44" s="6"/>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="6"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="6"/>
-      <c r="I44" s="6"/>
-      <c r="J44" s="6"/>
-      <c r="K44" s="6"/>
-      <c r="L44" s="6"/>
-      <c r="M44" s="6"/>
-      <c r="N44" s="6"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+      <c r="I44" s="5"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="5"/>
+      <c r="L44" s="5"/>
+      <c r="M44" s="5"/>
+      <c r="N44" s="5"/>
     </row>
     <row r="45" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="6" t="s">
+      <c r="A45" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B45" s="6"/>
-      <c r="C45" s="6"/>
-      <c r="D45" s="6"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="6"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="6"/>
-      <c r="I45" s="6"/>
-      <c r="J45" s="6"/>
-      <c r="K45" s="6"/>
-      <c r="L45" s="6"/>
-      <c r="M45" s="6"/>
-      <c r="N45" s="6"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="5"/>
+      <c r="J45" s="5"/>
+      <c r="K45" s="5"/>
+      <c r="L45" s="5"/>
+      <c r="M45" s="5"/>
+      <c r="N45" s="5"/>
     </row>
     <row r="46" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="6" t="s">
+      <c r="A46" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B46" s="6"/>
-      <c r="C46" s="6"/>
-      <c r="D46" s="6"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="6"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="6"/>
-      <c r="I46" s="6"/>
-      <c r="J46" s="6"/>
-      <c r="K46" s="6"/>
-      <c r="L46" s="6"/>
-      <c r="M46" s="6"/>
-      <c r="N46" s="6"/>
+      <c r="B46" s="5"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="5"/>
+      <c r="K46" s="5"/>
+      <c r="L46" s="5"/>
+      <c r="M46" s="5"/>
+      <c r="N46" s="5"/>
     </row>
     <row r="47" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="6" t="s">
+      <c r="A47" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B47" s="6"/>
-      <c r="C47" s="6"/>
-      <c r="D47" s="6"/>
-      <c r="E47" s="6"/>
-      <c r="F47" s="6"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="6"/>
-      <c r="J47" s="6"/>
-      <c r="K47" s="6"/>
-      <c r="L47" s="6"/>
-      <c r="M47" s="6"/>
-      <c r="N47" s="6"/>
+      <c r="B47" s="5"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="5"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="5"/>
+      <c r="I47" s="5"/>
+      <c r="J47" s="5"/>
+      <c r="K47" s="5"/>
+      <c r="L47" s="5"/>
+      <c r="M47" s="5"/>
+      <c r="N47" s="5"/>
     </row>
     <row r="48" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="6" t="s">
+      <c r="A48" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B48" s="6"/>
-      <c r="C48" s="6"/>
-      <c r="D48" s="6"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="6"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="6"/>
-      <c r="J48" s="6"/>
-      <c r="K48" s="6"/>
-      <c r="L48" s="6"/>
-      <c r="M48" s="6"/>
-      <c r="N48" s="6"/>
+      <c r="B48" s="5"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="5"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="5"/>
+      <c r="I48" s="5"/>
+      <c r="J48" s="5"/>
+      <c r="K48" s="5"/>
+      <c r="L48" s="5"/>
+      <c r="M48" s="5"/>
+      <c r="N48" s="5"/>
     </row>
     <row r="49" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="6" t="s">
+      <c r="A49" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B49" s="6"/>
-      <c r="C49" s="6"/>
-      <c r="D49" s="6"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="6"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="6"/>
-      <c r="I49" s="6"/>
-      <c r="J49" s="6"/>
-      <c r="K49" s="6"/>
-      <c r="L49" s="6"/>
-      <c r="M49" s="6"/>
-      <c r="N49" s="6"/>
+      <c r="B49" s="5"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="5"/>
+      <c r="G49" s="5"/>
+      <c r="H49" s="5"/>
+      <c r="I49" s="5"/>
+      <c r="J49" s="5"/>
+      <c r="K49" s="5"/>
+      <c r="L49" s="5"/>
+      <c r="M49" s="5"/>
+      <c r="N49" s="5"/>
     </row>
     <row r="50" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="6" t="s">
+      <c r="A50" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B50" s="6"/>
-      <c r="C50" s="6"/>
-      <c r="D50" s="6"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="6"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="6"/>
-      <c r="J50" s="6"/>
-      <c r="K50" s="6"/>
-      <c r="L50" s="6"/>
-      <c r="M50" s="6"/>
-      <c r="N50" s="6"/>
+      <c r="B50" s="5"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="5"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="5"/>
+      <c r="I50" s="5"/>
+      <c r="J50" s="5"/>
+      <c r="K50" s="5"/>
+      <c r="L50" s="5"/>
+      <c r="M50" s="5"/>
+      <c r="N50" s="5"/>
     </row>
     <row r="51" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="6" t="s">
+      <c r="A51" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B51" s="6"/>
-      <c r="C51" s="6"/>
-      <c r="D51" s="6"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="6"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="6"/>
-      <c r="I51" s="6"/>
-      <c r="J51" s="6"/>
-      <c r="K51" s="6"/>
-      <c r="L51" s="6"/>
-      <c r="M51" s="6"/>
-      <c r="N51" s="6"/>
+      <c r="B51" s="5"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="5"/>
+      <c r="I51" s="5"/>
+      <c r="J51" s="5"/>
+      <c r="K51" s="5"/>
+      <c r="L51" s="5"/>
+      <c r="M51" s="5"/>
+      <c r="N51" s="5"/>
     </row>
     <row r="52" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="5" t="s">
+      <c r="A52" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B52" s="5"/>
-      <c r="C52" s="5"/>
-      <c r="D52" s="5"/>
-      <c r="E52" s="5"/>
-      <c r="F52" s="5"/>
-      <c r="G52" s="5"/>
-      <c r="H52" s="5"/>
-      <c r="I52" s="5"/>
-      <c r="J52" s="5"/>
-      <c r="K52" s="5"/>
-      <c r="L52" s="5"/>
-      <c r="M52" s="5"/>
-      <c r="N52" s="5"/>
+      <c r="B52" s="6"/>
+      <c r="C52" s="6"/>
+      <c r="D52" s="6"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="6"/>
+      <c r="G52" s="6"/>
+      <c r="H52" s="6"/>
+      <c r="I52" s="6"/>
+      <c r="J52" s="6"/>
+      <c r="K52" s="6"/>
+      <c r="L52" s="6"/>
+      <c r="M52" s="6"/>
+      <c r="N52" s="6"/>
     </row>
     <row r="53" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="6" t="s">
+      <c r="A53" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B53" s="6"/>
-      <c r="C53" s="6"/>
-      <c r="D53" s="6"/>
-      <c r="E53" s="6"/>
-      <c r="F53" s="6"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="6"/>
-      <c r="I53" s="6"/>
-      <c r="J53" s="6"/>
-      <c r="K53" s="6"/>
-      <c r="L53" s="6"/>
-      <c r="M53" s="6"/>
-      <c r="N53" s="6"/>
+      <c r="B53" s="5"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="5"/>
+      <c r="E53" s="5"/>
+      <c r="F53" s="5"/>
+      <c r="G53" s="5"/>
+      <c r="H53" s="5"/>
+      <c r="I53" s="5"/>
+      <c r="J53" s="5"/>
+      <c r="K53" s="5"/>
+      <c r="L53" s="5"/>
+      <c r="M53" s="5"/>
+      <c r="N53" s="5"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="6" t="s">
+      <c r="A54" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B54" s="6"/>
-      <c r="C54" s="6"/>
-      <c r="D54" s="6"/>
-      <c r="E54" s="6"/>
-      <c r="F54" s="6"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="6"/>
-      <c r="I54" s="6"/>
-      <c r="J54" s="6"/>
-      <c r="K54" s="6"/>
-      <c r="L54" s="6"/>
-      <c r="M54" s="6"/>
-      <c r="N54" s="6"/>
+      <c r="B54" s="5"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="5"/>
+      <c r="E54" s="5"/>
+      <c r="F54" s="5"/>
+      <c r="G54" s="5"/>
+      <c r="H54" s="5"/>
+      <c r="I54" s="5"/>
+      <c r="J54" s="5"/>
+      <c r="K54" s="5"/>
+      <c r="L54" s="5"/>
+      <c r="M54" s="5"/>
+      <c r="N54" s="5"/>
     </row>
     <row r="55" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="6" t="s">
+      <c r="A55" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B55" s="6"/>
-      <c r="C55" s="6"/>
-      <c r="D55" s="6"/>
-      <c r="E55" s="6"/>
-      <c r="F55" s="6"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="6"/>
-      <c r="I55" s="6"/>
-      <c r="J55" s="6"/>
-      <c r="K55" s="6"/>
-      <c r="L55" s="6"/>
-      <c r="M55" s="6"/>
-      <c r="N55" s="6"/>
+      <c r="B55" s="5"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="5"/>
+      <c r="E55" s="5"/>
+      <c r="F55" s="5"/>
+      <c r="G55" s="5"/>
+      <c r="H55" s="5"/>
+      <c r="I55" s="5"/>
+      <c r="J55" s="5"/>
+      <c r="K55" s="5"/>
+      <c r="L55" s="5"/>
+      <c r="M55" s="5"/>
+      <c r="N55" s="5"/>
     </row>
     <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/agriculture 46.xlsx
+++ b/agriculture 46.xlsx
@@ -181,7 +181,7 @@
     <t xml:space="preserve">2020-21</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit:- Percentage(%)</t>
+    <t xml:space="preserve">Unit:- Percentage (%)</t>
   </si>
   <si>
     <r>
@@ -437,7 +437,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N1048576"/>
-  <sheetFormatPr defaultColWidth="10.8125" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.82421875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
